--- a/.cursor/scratch/tax_turbo_parts/HOME_SPLIT.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/HOME_SPLIT.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>March Home Depot 100% → 524 repairs, then 50/50 Unit 1 / Unit 2. Each remaining txn split 1/3 524 / 1/3 personal / 1/3 827 Grove; leftover pennies to 524 then personal. 524 third then 50/50 (extra penny to Unit 2). Not tax advice.</t>
+          <t>March Home Depot 100% → 524 repairs, then 50/50 Unit 1 / Unit 2. Each remaining txn split 1/3 524 / 1/3 personal / 1/3 827 N Grove the house (NOT Grove Collaborative); leftover pennies to 524 then personal. 524 third then 50/50 (extra penny to Unit 2). Not tax advice.</t>
         </is>
       </c>
     </row>
